--- a/output/出貨單-台鑫堆高機有限公司-20260506.xlsx
+++ b/output/出貨單-台鑫堆高機有限公司-20260506.xlsx
@@ -582,10 +582,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1212,7 +1212,7 @@
       <c r="B10" s="65" t="n"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Hector</t>
+          <t>小皋</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -1240,33 +1240,37 @@
       <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="inlineStr">
-        <is>
-          <t>□發票隨貨</t>
-        </is>
-      </c>
-      <c r="B12" s="68" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="68" t="n"/>
-      <c r="E12" s="68" t="n"/>
-      <c r="F12" s="68" t="n"/>
-      <c r="G12" s="68" t="n"/>
-      <c r="H12" s="68" t="n"/>
-      <c r="I12" s="68" t="n"/>
-      <c r="J12" s="68" t="n"/>
+      <c r="A12" s="67" t="n"/>
+      <c r="B12" s="67" t="n"/>
+      <c r="C12" s="67" t="n"/>
+      <c r="D12" s="67" t="n"/>
+      <c r="E12" s="67" t="n"/>
+      <c r="F12" s="67" t="n"/>
+      <c r="G12" s="67" t="n"/>
+      <c r="H12" s="67" t="n"/>
+      <c r="I12" s="68" t="inlineStr">
+        <is>
+          <t>■發票隨貨</t>
+        </is>
+      </c>
+      <c r="J12" s="68" t="inlineStr">
+        <is>
+          <t>□發票直寄</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="n"/>
-      <c r="B13" s="68" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="68" t="n"/>
-      <c r="E13" s="68" t="n"/>
-      <c r="F13" s="68" t="n"/>
-      <c r="G13" s="68" t="n"/>
-      <c r="H13" s="68" t="n"/>
-      <c r="I13" s="68" t="n"/>
-      <c r="J13" s="68" t="n"/>
+      <c r="A13" s="67" t="n"/>
+      <c r="B13" s="67" t="n"/>
+      <c r="C13" s="67" t="n"/>
+      <c r="D13" s="67" t="n"/>
+      <c r="E13" s="67" t="n"/>
+      <c r="F13" s="67" t="n"/>
+      <c r="G13" s="67" t="n"/>
+      <c r="H13" s="67" t="n"/>
+      <c r="I13" s="67" t="n"/>
+      <c r="J13" s="67" t="n"/>
       <c r="L13" s="4" t="n"/>
     </row>
   </sheetData>
